--- a/data/pinjaman.xlsx
+++ b/data/pinjaman.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -620,6 +620,62 @@
       </c>
       <c r="N3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>83ae658b-af2a-41f1-8416-11233254114f</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AGT-15612551561</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>hayuk</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AGT-0006</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Import CSV</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>5105450</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5738525.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>441425.06</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5738525.8</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/pinjaman.xlsx
+++ b/data/pinjaman.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -425,15 +425,17 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,45 +466,55 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>jenis_simpanan</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>plafon</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tenor_awal</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tenor_bulan</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>bunga_persen</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total_bayar</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>cicilan_per_bulan</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>sisa_pinjaman</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>tanggal_pengajuan</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>tanggal_lunas</t>
         </is>
@@ -511,170 +523,198 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>778f91a1-8765-4b8a-b459-df306e3918bd</t>
+          <t>818c78aa-207f-4391-baa3-84113c97f8c7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>582f9a5f-a0c9-4737-a724-1fd6f9307798</t>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>shidqi</t>
+          <t>Siti Aulia</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AGT-0002</t>
+          <t>AGT-020</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jangka Panjang</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>310000000</v>
+          <t>Solusi Cepat</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Manasuka</t>
+        </is>
       </c>
       <c r="G2" t="n">
-        <v>120</v>
+        <v>3000000</v>
       </c>
       <c r="H2" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>589000000</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4908333.33</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>589000000</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Disetujui</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>3060000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1560000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Lunas</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6f3dd9c2-229d-4a49-821d-0900751361f9</t>
+          <t>a5e9aacf-67b1-427f-a637-ae6b305d928d</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>582f9a5f-a0c9-4737-a724-1fd6f9307798</t>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>shidqi</t>
+          <t>Siti Aulia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AGT-0002</t>
+          <t>AGT-020</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jangka Pendek</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>6000000</v>
+          <t>Jangka Panjang</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Manasuka</t>
+        </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>3000000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
-        <v>6450000</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>1290000</v>
+        <v>0.8</v>
       </c>
       <c r="K3" t="n">
-        <v>6450000</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+        <v>3516000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>174000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>83ae658b-af2a-41f1-8416-11233254114f</t>
+          <t>83e839bc-9a6d-4c81-9c34-230b337d794d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AGT-15612551561</t>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hayuk</t>
+          <t>Siti Aulia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AGT-0006</t>
+          <t>AGT-020</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Import CSV</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>5105450</v>
+          <t>Modal Usaha</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Manasuka</t>
+        </is>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>103000000</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>24</v>
       </c>
       <c r="I4" t="n">
-        <v>5738525.8</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>441425.06</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>5738525.8</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+        <v>114845000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5665000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>92668333.33</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/pinjaman.xlsx
+++ b/data/pinjaman.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -716,6 +716,210 @@
       </c>
       <c r="P4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>f367c691-a2f0-4d53-9ab4-5245da1d2c79</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Solusi Cepat</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Manasuka</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3060000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1560000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Lunas</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>a1e62512-e12c-4c9e-8c6e-46e66d6defd9</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Solusi Cepat</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Manasuka</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3060000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1560000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Lunas</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Solusi Cepat</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Manasuka</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3120000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1560000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Lunas</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/pinjaman.xlsx
+++ b/data/pinjaman.xlsx
@@ -426,7 +426,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
@@ -523,22 +523,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>818c78aa-207f-4391-baa3-84113c97f8c7</t>
+          <t>7aafe11b-5228-484a-9fe8-3b29d45a6677</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -564,7 +564,7 @@
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>3060000</v>
+        <v>3120000</v>
       </c>
       <c r="L2" t="n">
         <v>1560000</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -584,34 +584,34 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>a5e9aacf-67b1-427f-a637-ae6b305d928d</t>
+          <t>739be525-a36b-496b-9d13-8415f2f8a211</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jangka Panjang</t>
+          <t>Jangka Pendek</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -623,59 +623,63 @@
         <v>3000000</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3516000</v>
+        <v>3225000</v>
       </c>
       <c r="L3" t="n">
-        <v>174000</v>
+        <v>545000</v>
       </c>
       <c r="M3" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Disetujui</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+          <t>Lunas</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>83e839bc-9a6d-4c81-9c34-230b337d794d</t>
+          <t>7f58a662-a9dd-45db-b0fb-0a4973fd7848</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Modal Usaha</t>
+          <t>Jangka Pendek</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -684,62 +688,66 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>103000000</v>
+        <v>3000000</v>
       </c>
       <c r="H4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="K4" t="n">
-        <v>114845000</v>
+        <v>3405000</v>
       </c>
       <c r="L4" t="n">
-        <v>5665000</v>
+        <v>345000</v>
       </c>
       <c r="M4" t="n">
-        <v>92668333.33</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Disetujui</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
+          <t>Lunas</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>f367c691-a2f0-4d53-9ab4-5245da1d2c79</t>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Septiawan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-001</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Solusi Cepat</t>
+          <t>Jangka Panjang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -748,29 +756,29 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3000000</v>
+        <v>55555555</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3060000</v>
+        <v>65111110.46</v>
       </c>
       <c r="L5" t="n">
-        <v>1560000</v>
+        <v>3222222.19</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -780,34 +788,34 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>a1e62512-e12c-4c9e-8c6e-46e66d6defd9</t>
+          <t>ee8f7075-b565-4c35-84d0-7fb11bc88f80</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Septiawan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-001</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Solusi Cepat</t>
+          <t>Modal Usaha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -816,66 +824,62 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3000000</v>
+        <v>1000000000</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3060000</v>
+        <v>1265000000</v>
       </c>
       <c r="L6" t="n">
-        <v>1560000</v>
+        <v>25000000</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>975000000</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Lunas</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+          <t>6990664e-e01f-43aa-ad8a-cc0d8c1ff238</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Solusi Cepat</t>
+          <t>Jangka Panjang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -884,41 +888,37 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3000000</v>
+        <v>55555555</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="K7" t="n">
-        <v>3120000</v>
+        <v>66666666</v>
       </c>
       <c r="L7" t="n">
-        <v>1560000</v>
+        <v>2638888.86</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>50277777.28</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Lunas</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/pinjaman.xlsx
+++ b/data/pinjaman.xlsx
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3000000</v>
+        <v>6000000</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -632,10 +632,10 @@
         <v>1.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3225000</v>
+        <v>6000000</v>
       </c>
       <c r="L3" t="n">
-        <v>545000</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -659,27 +659,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7f58a662-a9dd-45db-b0fb-0a4973fd7848</t>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boseng</t>
+          <t>Septiawan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AGT-065</t>
+          <t>AGT-001</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jangka Pendek</t>
+          <t>Jangka Panjang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -688,22 +688,22 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3000000</v>
+        <v>55555555</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="K4" t="n">
-        <v>3405000</v>
+        <v>65111110.46</v>
       </c>
       <c r="L4" t="n">
-        <v>345000</v>
+        <v>3222222.19</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -727,7 +727,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+          <t>ee8f7075-b565-4c35-84d0-7fb11bc88f80</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jangka Panjang</t>
+          <t>Modal Usaha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -756,25 +756,25 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>55555555</v>
+        <v>1000000000</v>
       </c>
       <c r="H5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>65111110.46</v>
+        <v>1265000000</v>
       </c>
       <c r="L5" t="n">
-        <v>3222222.19</v>
+        <v>25000000</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>975000000</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -783,39 +783,35 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Lunas</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ee8f7075-b565-4c35-84d0-7fb11bc88f80</t>
+          <t>6990664e-e01f-43aa-ad8a-cc0d8c1ff238</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Septiawan</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AGT-001</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Modal Usaha</t>
+          <t>Jangka Panjang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -824,25 +820,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1000000000</v>
+        <v>55555555</v>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I6" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K6" t="n">
-        <v>1265000000</v>
+        <v>66666666</v>
       </c>
       <c r="L6" t="n">
-        <v>25000000</v>
+        <v>2638888.86</v>
       </c>
       <c r="M6" t="n">
-        <v>975000000</v>
+        <v>50277777.28</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -859,22 +855,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6990664e-e01f-43aa-ad8a-cc0d8c1ff238</t>
+          <t>48bbfd56-6a50-4b0a-aea8-d8692f358d0f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+          <t>02b98d05-e120-42e8-81b2-1fe8887d5c70</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boseng</t>
+          <t>Budi Santoso</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AGT-065</t>
+          <t>AG0001</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -882,35 +878,31 @@
           <t>Jangka Panjang</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Manasuka</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>55555555</v>
+        <v>40000000</v>
       </c>
       <c r="H7" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I7" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="J7" t="n">
         <v>0.75</v>
       </c>
       <c r="K7" t="n">
-        <v>66666666</v>
+        <v>52500000</v>
       </c>
       <c r="L7" t="n">
-        <v>2638888.86</v>
+        <v>1300000</v>
       </c>
       <c r="M7" t="n">
-        <v>50277777.28</v>
+        <v>40000000</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">

--- a/data/pinjaman.xlsx
+++ b/data/pinjaman.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
@@ -434,7 +434,7 @@
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -523,27 +523,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7aafe11b-5228-484a-9fe8-3b29d45a6677</t>
+          <t>9d80ef55-4a26-4154-bb6a-8e404784f616</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+          <t>AGT-DEMO-001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boseng</t>
+          <t>Anggota Demo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AGT-065</t>
+          <t>KOP-0001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Solusi Cepat</t>
+          <t>Jangka Pendek</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,362 +555,34 @@
         <v>3000000</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3120000</v>
+        <v>3540000</v>
       </c>
       <c r="L2" t="n">
-        <v>1560000</v>
+        <v>295000</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3540000</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Lunas</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>739be525-a36b-496b-9d13-8415f2f8a211</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Boseng</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>AGT-065</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Jangka Pendek</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Manasuka</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Lunas</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Septiawan</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AGT-001</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Jangka Panjang</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Manasuka</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>55555555</v>
-      </c>
-      <c r="H4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>65111110.46</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3222222.19</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Lunas</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ee8f7075-b565-4c35-84d0-7fb11bc88f80</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Septiawan</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AGT-001</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Modal Usaha</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Manasuka</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>50</v>
-      </c>
-      <c r="I5" t="n">
-        <v>49</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1265000000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>975000000</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Disetujui</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>6990664e-e01f-43aa-ad8a-cc0d8c1ff238</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Boseng</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AGT-065</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Jangka Panjang</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Manasuka</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>55555555</v>
-      </c>
-      <c r="H6" t="n">
-        <v>25</v>
-      </c>
-      <c r="I6" t="n">
-        <v>23</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K6" t="n">
-        <v>66666666</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2638888.86</v>
-      </c>
-      <c r="M6" t="n">
-        <v>50277777.28</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Disetujui</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>48bbfd56-6a50-4b0a-aea8-d8692f358d0f</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>02b98d05-e120-42e8-81b2-1fe8887d5c70</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Budi Santoso</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>AG0001</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Jangka Panjang</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>40</v>
-      </c>
-      <c r="I7" t="n">
-        <v>40</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K7" t="n">
-        <v>52500000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="M7" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Disetujui</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
+          <t>Menunggu Persetujuan</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/pinjaman.xlsx
+++ b/data/pinjaman.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -523,27 +523,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9d80ef55-4a26-4154-bb6a-8e404784f616</t>
+          <t>d453c433-d6bc-4c58-b811-5d54b7331a90</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGT-DEMO-001</t>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Anggota Demo</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KOP-0001</t>
+          <t>AGT-001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jangka Pendek</t>
+          <t>Jangka Panjang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,34 +555,98 @@
         <v>3000000</v>
       </c>
       <c r="H2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3372000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>238285.71</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Menunggu</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ada754c8-4996-40de-9a0e-1ca4126e223b</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AGT-DEMO-001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Anggota Demo</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>KOP-0001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Jangka Pendek</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Manasuka</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H3" t="n">
         <v>12</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I3" t="n">
         <v>12</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J3" t="n">
         <v>1.5</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K3" t="n">
         <v>3540000</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L3" t="n">
         <v>295000</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M3" t="n">
         <v>3540000</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>Menunggu Persetujuan</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/pinjaman.xlsx
+++ b/data/pinjaman.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -558,7 +558,7 @@
         <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
         <v>0.8</v>
@@ -570,7 +570,7 @@
         <v>238285.71</v>
       </c>
       <c r="M2" t="n">
-        <v>3000000</v>
+        <v>2523428.58</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Menunggu</t>
+          <t>Disetujui</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -647,6 +647,70 @@
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>c012c367-b8fe-4964-b89e-0f0478e3d31a</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Jangka Pendek</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Manasuka</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3090000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1045000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Menunggu</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/pinjaman.xlsx
+++ b/data/pinjaman.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Menunggu</t>
+          <t>Disetujui</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>

--- a/data/pinjaman.xlsx
+++ b/data/pinjaman.xlsx
@@ -426,7 +426,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3000000</v>
+        <v>103000000</v>
       </c>
       <c r="H2" t="n">
         <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="J2" t="n">
         <v>0.8</v>
       </c>
       <c r="K2" t="n">
-        <v>3372000</v>
+        <v>129007500</v>
       </c>
       <c r="L2" t="n">
-        <v>238285.71</v>
+        <v>3991250</v>
       </c>
       <c r="M2" t="n">
-        <v>2523428.58</v>
+        <v>98532178.58</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>

--- a/data/pinjaman.xlsx
+++ b/data/pinjaman.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>103000000</v>
+        <v>133000000</v>
       </c>
       <c r="H2" t="n">
         <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J2" t="n">
         <v>0.8</v>
       </c>
       <c r="K2" t="n">
-        <v>129007500</v>
+        <v>163590000</v>
       </c>
       <c r="L2" t="n">
-        <v>3991250</v>
+        <v>5583706.9</v>
       </c>
       <c r="M2" t="n">
-        <v>98532178.58</v>
+        <v>128532178.58</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -680,37 +680,221 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3000000</v>
+        <v>13000000</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>1.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3090000</v>
+        <v>14365000</v>
       </c>
       <c r="L4" t="n">
-        <v>1045000</v>
+        <v>1820000</v>
       </c>
       <c r="M4" t="n">
+        <v>5720000</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>b59dca00-0471-448f-a0f6-b954f8a658dd</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AGT-DEMO-001</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>KOP-0001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Jangka Panjang</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Manasuka</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>29</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12300000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>419827.59</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Lunas</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>8ab14b82-442f-4b20-9f3d-245c2c745bea</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AGT-DEMO-001</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>KOP-0001</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Jangka Panjang</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Manasuka</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" t="n">
+        <v>27</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K6" t="n">
+        <v>12375000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>408333.33</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8775000.01</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>410d9453-ca66-4822-92c3-f63e684ba97b</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Solusi Cepat</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Manasuka</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>3000000</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3060000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3060000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
